--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenGroup.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenGroup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_equip_strengthGroup" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="224">
   <si>
     <t>序列</t>
   </si>
@@ -119,22 +119,22 @@
     <t>201021#27|201011#27</t>
   </si>
   <si>
-    <t>201021#31|201011#31</t>
+    <t>201021#30|201011#30</t>
+  </si>
+  <si>
+    <t>201021#33|201011#33</t>
   </si>
   <si>
     <t>201021#36|201011#36</t>
   </si>
   <si>
+    <t>201021#39|201011#39</t>
+  </si>
+  <si>
     <t>201021#42|201011#42</t>
   </si>
   <si>
-    <t>201021#49|201011#49</t>
-  </si>
-  <si>
-    <t>201021#57|201011#57</t>
-  </si>
-  <si>
-    <t>201021#66|201011#66</t>
+    <t>201021#45|201011#45</t>
   </si>
   <si>
     <t>魔法攻击</t>
@@ -152,37 +152,37 @@
     <t>201021#12|201011#12|202042#1400</t>
   </si>
   <si>
-    <t>201021#15|201011#15|202042#1700</t>
+    <t>201021#15|201011#15|202042#1800</t>
   </si>
   <si>
     <t>201021#18|201011#18|202042#2100</t>
   </si>
   <si>
-    <t>201021#21|201011#21|202042#2400</t>
-  </si>
-  <si>
-    <t>201021#24|201011#24|202042#2800</t>
-  </si>
-  <si>
-    <t>201021#27|201011#27|202042#3100</t>
-  </si>
-  <si>
-    <t>201021#31|201011#31|202042#3500</t>
-  </si>
-  <si>
-    <t>201021#36|201011#36|202042#4000</t>
-  </si>
-  <si>
-    <t>201021#42|201011#42|202042#4500</t>
-  </si>
-  <si>
-    <t>201021#49|201011#49|202042#5000</t>
-  </si>
-  <si>
-    <t>201021#57|201011#57|202042#5600</t>
-  </si>
-  <si>
-    <t>201021#66|201011#66|202042#6300</t>
+    <t>201021#21|201011#21|202042#2500</t>
+  </si>
+  <si>
+    <t>201021#24|201011#24|202042#2900</t>
+  </si>
+  <si>
+    <t>201021#27|201011#27|202042#3300</t>
+  </si>
+  <si>
+    <t>201021#30|201011#30|202042#3600</t>
+  </si>
+  <si>
+    <t>201021#36|201011#36|202042#4100</t>
+  </si>
+  <si>
+    <t>201021#39|201011#39|202042#4700</t>
+  </si>
+  <si>
+    <t>201021#42|201011#42|202042#5200</t>
+  </si>
+  <si>
+    <t>201021#45|201011#45|202042#5800</t>
+  </si>
+  <si>
+    <t>201021#50|201011#50|202042#6500</t>
   </si>
   <si>
     <t>防御</t>
@@ -215,40 +215,28 @@
     <t>206011#27</t>
   </si>
   <si>
-    <t>206011#31</t>
+    <t>206011#30</t>
+  </si>
+  <si>
+    <t>206011#33</t>
   </si>
   <si>
     <t>206011#36</t>
   </si>
   <si>
+    <t>206011#39</t>
+  </si>
+  <si>
     <t>206011#42</t>
   </si>
   <si>
-    <t>206011#49</t>
-  </si>
-  <si>
-    <t>206011#57</t>
-  </si>
-  <si>
-    <t>206011#66</t>
+    <t>206011#45</t>
   </si>
   <si>
     <t>翅膀物理</t>
   </si>
   <si>
-    <t>206011#37</t>
-  </si>
-  <si>
-    <t>206011#46</t>
-  </si>
-  <si>
-    <t>206011#59</t>
-  </si>
-  <si>
-    <t>206011#77</t>
-  </si>
-  <si>
-    <t>206011#101</t>
+    <t>206011#50</t>
   </si>
   <si>
     <t>翅膀魔法</t>
@@ -269,34 +257,34 @@
     <t>202011#5|202021#3</t>
   </si>
   <si>
-    <t>202011#6|202021#4</t>
-  </si>
-  <si>
-    <t>202011#8|202021#5</t>
-  </si>
-  <si>
-    <t>202011#10|202021#6</t>
-  </si>
-  <si>
-    <t>202011#12|202021#7</t>
-  </si>
-  <si>
-    <t>202011#14|202021#8</t>
-  </si>
-  <si>
-    <t>202011#16|202021#10</t>
-  </si>
-  <si>
-    <t>202011#18|202021#11</t>
-  </si>
-  <si>
-    <t>202011#20|202021#12</t>
-  </si>
-  <si>
-    <t>202011#22|202021#13</t>
-  </si>
-  <si>
-    <t>202011#24|202021#14</t>
+    <t>202011#6|202021#3</t>
+  </si>
+  <si>
+    <t>202011#7|202021#5</t>
+  </si>
+  <si>
+    <t>202011#9|202021#5</t>
+  </si>
+  <si>
+    <t>202011#11|202021#7</t>
+  </si>
+  <si>
+    <t>202011#13|202021#9</t>
+  </si>
+  <si>
+    <t>202011#15|202021#10</t>
+  </si>
+  <si>
+    <t>202011#17|202021#11</t>
+  </si>
+  <si>
+    <t>202011#19|202021#12</t>
+  </si>
+  <si>
+    <t>202011#21|202021#13</t>
+  </si>
+  <si>
+    <t>202011#25|202021#15</t>
   </si>
   <si>
     <t>首饰强化（防御）</t>
@@ -353,22 +341,22 @@
     <t>206011#27|318022#500</t>
   </si>
   <si>
-    <t>206011#31|318022#500</t>
+    <t>206011#30|318022#500</t>
+  </si>
+  <si>
+    <t>206011#33|318022#500</t>
   </si>
   <si>
     <t>206011#36|318022#500</t>
   </si>
   <si>
+    <t>206011#39|318022#500</t>
+  </si>
+  <si>
     <t>206011#42|318022#500</t>
   </si>
   <si>
-    <t>206011#49|318022#500</t>
-  </si>
-  <si>
-    <t>206011#57|318022#500</t>
-  </si>
-  <si>
-    <t>206011#66|318022#500</t>
+    <t>206011#50|318022#500</t>
   </si>
   <si>
     <t>鞋子</t>
@@ -377,49 +365,49 @@
     <t>首饰强化（攻击）</t>
   </si>
   <si>
-    <t>200011#1|200021#1</t>
-  </si>
-  <si>
     <t>200011#1|200021#2</t>
   </si>
   <si>
-    <t>200011#2|200021#3</t>
-  </si>
-  <si>
-    <t>200011#2|200021#4</t>
-  </si>
-  <si>
-    <t>200011#3|200021#5</t>
-  </si>
-  <si>
-    <t>200011#4|200021#6</t>
-  </si>
-  <si>
-    <t>200011#5|200021#8</t>
+    <t>200011#1|200021#4</t>
+  </si>
+  <si>
+    <t>200011#2|200021#5</t>
+  </si>
+  <si>
+    <t>200011#2|200021#6</t>
+  </si>
+  <si>
+    <t>200011#3|200021#7</t>
+  </si>
+  <si>
+    <t>200011#4|200021#8</t>
+  </si>
+  <si>
+    <t>200011#5|200021#9</t>
   </si>
   <si>
     <t>200011#6|200021#10</t>
   </si>
   <si>
-    <t>200011#7|200021#12</t>
-  </si>
-  <si>
-    <t>200011#8|200021#14</t>
-  </si>
-  <si>
-    <t>200011#10|200021#16</t>
-  </si>
-  <si>
-    <t>200011#11|200021#18</t>
-  </si>
-  <si>
-    <t>200011#12|200021#20</t>
-  </si>
-  <si>
-    <t>200011#13|200021#22</t>
-  </si>
-  <si>
-    <t>200011#14|200021#24</t>
+    <t>200011#7|200021#11</t>
+  </si>
+  <si>
+    <t>200011#8|200021#13</t>
+  </si>
+  <si>
+    <t>200011#10|200021#15</t>
+  </si>
+  <si>
+    <t>200011#11|200021#17</t>
+  </si>
+  <si>
+    <t>200011#12|200021#19</t>
+  </si>
+  <si>
+    <t>200011#13|200021#21</t>
+  </si>
+  <si>
+    <t>200011#14|200021#23</t>
   </si>
   <si>
     <t>翅膀强化类型1</t>
@@ -644,22 +632,22 @@
     <t>206011#27|211011#9</t>
   </si>
   <si>
-    <t>206011#31|211011#10</t>
-  </si>
-  <si>
-    <t>206011#36|211011#11</t>
-  </si>
-  <si>
-    <t>206011#42|211011#12</t>
-  </si>
-  <si>
-    <t>206011#49|211011#13</t>
-  </si>
-  <si>
-    <t>206011#57|211011#14</t>
-  </si>
-  <si>
-    <t>206011#66|211011#15</t>
+    <t>206011#30|211011#10</t>
+  </si>
+  <si>
+    <t>206011#33|211011#11</t>
+  </si>
+  <si>
+    <t>206011#36|211011#12</t>
+  </si>
+  <si>
+    <t>206011#39|211011#13</t>
+  </si>
+  <si>
+    <t>206011#42|211011#14</t>
+  </si>
+  <si>
+    <t>206011#45|211011#15</t>
   </si>
   <si>
     <t>翅膀强化类型5</t>
@@ -2805,7 +2793,7 @@
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2822,7 +2810,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2839,7 +2827,7 @@
         <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2856,7 +2844,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2873,7 +2861,7 @@
         <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2884,13 +2872,13 @@
         <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2901,13 +2889,13 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D66">
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2918,13 +2906,13 @@
         <v>5</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2935,13 +2923,13 @@
         <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D68">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2952,13 +2940,13 @@
         <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D69">
         <v>5</v>
       </c>
       <c r="E69" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2969,13 +2957,13 @@
         <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D70">
         <v>6</v>
       </c>
       <c r="E70" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2986,13 +2974,13 @@
         <v>5</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D71">
         <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3003,13 +2991,13 @@
         <v>5</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D72">
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3020,13 +3008,13 @@
         <v>5</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D73">
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3037,13 +3025,13 @@
         <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D74">
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3054,13 +3042,13 @@
         <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D75">
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3071,13 +3059,13 @@
         <v>5</v>
       </c>
       <c r="C76" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D76">
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3088,13 +3076,13 @@
         <v>5</v>
       </c>
       <c r="C77" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D77">
         <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3105,13 +3093,13 @@
         <v>5</v>
       </c>
       <c r="C78" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D78">
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3122,13 +3110,13 @@
         <v>5</v>
       </c>
       <c r="C79" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D79">
         <v>15</v>
       </c>
       <c r="E79" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" ht="14.25" spans="1:6">
@@ -3139,16 +3127,16 @@
         <v>6</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81" ht="14.25" spans="1:6">
@@ -3159,16 +3147,16 @@
         <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D81">
         <v>2</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82" ht="14.25" spans="1:6">
@@ -3179,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -3188,7 +3176,7 @@
         <v>53</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" ht="14.25" spans="1:6">
@@ -3199,16 +3187,16 @@
         <v>6</v>
       </c>
       <c r="C83" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D83">
         <v>4</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" ht="14.25" spans="1:6">
@@ -3219,16 +3207,16 @@
         <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D84">
         <v>5</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="85" ht="14.25" spans="1:6">
@@ -3239,7 +3227,7 @@
         <v>6</v>
       </c>
       <c r="C85" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D85">
         <v>6</v>
@@ -3248,7 +3236,7 @@
         <v>54</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" ht="14.25" spans="1:6">
@@ -3259,16 +3247,16 @@
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D86">
         <v>7</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" ht="14.25" spans="1:6">
@@ -3279,16 +3267,16 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D87">
         <v>8</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" ht="14.25" spans="1:6">
@@ -3299,7 +3287,7 @@
         <v>6</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D88">
         <v>9</v>
@@ -3308,7 +3296,7 @@
         <v>55</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" ht="14.25" spans="1:6">
@@ -3319,16 +3307,16 @@
         <v>6</v>
       </c>
       <c r="C89" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D89">
         <v>10</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" ht="14.25" spans="1:6">
@@ -3339,16 +3327,16 @@
         <v>6</v>
       </c>
       <c r="C90" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D90">
         <v>11</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" ht="14.25" spans="1:6">
@@ -3359,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D91">
         <v>12</v>
@@ -3368,7 +3356,7 @@
         <v>57</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" ht="14.25" spans="1:6">
@@ -3379,16 +3367,16 @@
         <v>6</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D92">
         <v>13</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" ht="14.25" spans="1:6">
@@ -3399,16 +3387,16 @@
         <v>6</v>
       </c>
       <c r="C93" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D93">
         <v>14</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" ht="14.25" spans="1:6">
@@ -3419,7 +3407,7 @@
         <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D94">
         <v>15</v>
@@ -3428,7 +3416,7 @@
         <v>59</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" ht="14.25" spans="1:6">
@@ -3439,7 +3427,7 @@
         <v>7</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D95" s="4">
         <v>1</v>
@@ -3456,7 +3444,7 @@
         <v>7</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D96" s="4">
         <v>2</v>
@@ -3473,7 +3461,7 @@
         <v>7</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D97" s="4">
         <v>3</v>
@@ -3490,7 +3478,7 @@
         <v>7</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D98" s="4">
         <v>4</v>
@@ -3507,13 +3495,13 @@
         <v>7</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D99" s="4">
         <v>5</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" ht="14.25" spans="1:5">
@@ -3524,13 +3512,13 @@
         <v>7</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D100" s="4">
         <v>6</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" ht="14.25" spans="1:5">
@@ -3541,13 +3529,13 @@
         <v>7</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D101" s="4">
         <v>7</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" ht="14.25" spans="1:5">
@@ -3558,13 +3546,13 @@
         <v>7</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D102" s="4">
         <v>8</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" ht="14.25" spans="1:5">
@@ -3575,13 +3563,13 @@
         <v>7</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D103" s="4">
         <v>9</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="104" ht="14.25" spans="1:5">
@@ -3592,13 +3580,13 @@
         <v>7</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D104" s="4">
         <v>10</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" ht="14.25" spans="1:5">
@@ -3609,13 +3597,13 @@
         <v>7</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D105" s="4">
         <v>11</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="106" ht="14.25" spans="1:5">
@@ -3626,13 +3614,13 @@
         <v>7</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D106" s="4">
         <v>12</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" ht="14.25" spans="1:5">
@@ -3643,13 +3631,13 @@
         <v>7</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D107" s="4">
         <v>13</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" ht="14.25" spans="1:5">
@@ -3660,13 +3648,13 @@
         <v>7</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D108" s="4">
         <v>14</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" ht="14.25" spans="1:5">
@@ -3677,13 +3665,13 @@
         <v>7</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D109" s="4">
         <v>15</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" ht="14.25" spans="1:5">
@@ -3694,7 +3682,7 @@
         <v>8</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D110" s="4">
         <v>1</v>
@@ -3711,7 +3699,7 @@
         <v>8</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D111" s="4">
         <v>2</v>
@@ -3728,7 +3716,7 @@
         <v>8</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D112" s="4">
         <v>3</v>
@@ -3745,7 +3733,7 @@
         <v>8</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D113" s="4">
         <v>4</v>
@@ -3762,13 +3750,13 @@
         <v>8</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D114" s="4">
         <v>5</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" ht="14.25" spans="1:6">
@@ -3779,13 +3767,13 @@
         <v>8</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D115" s="4">
         <v>6</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" ht="14.25" spans="1:6">
@@ -3796,13 +3784,13 @@
         <v>8</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D116" s="4">
         <v>7</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="117" ht="14.25" spans="1:6">
@@ -3813,13 +3801,13 @@
         <v>8</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D117" s="4">
         <v>8</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="118" ht="14.25" spans="1:6">
@@ -3830,13 +3818,13 @@
         <v>8</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D118" s="4">
         <v>9</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119" ht="14.25" spans="1:6">
@@ -3847,13 +3835,13 @@
         <v>8</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D119" s="4">
         <v>10</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="120" ht="14.25" spans="1:6">
@@ -3864,13 +3852,13 @@
         <v>8</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D120" s="4">
         <v>11</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" ht="14.25" spans="1:6">
@@ -3881,13 +3869,13 @@
         <v>8</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D121" s="4">
         <v>12</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="122" ht="14.25" spans="1:6">
@@ -3898,13 +3886,13 @@
         <v>8</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D122" s="4">
         <v>13</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" ht="14.25" spans="1:6">
@@ -3915,13 +3903,13 @@
         <v>8</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D123" s="4">
         <v>14</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" ht="14.25" spans="1:6">
@@ -3932,13 +3920,13 @@
         <v>8</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D124" s="4">
         <v>15</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="125" ht="14.25" spans="1:6">
@@ -3949,16 +3937,16 @@
         <v>9</v>
       </c>
       <c r="C125" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="126" ht="14.25" spans="1:6">
@@ -3969,16 +3957,16 @@
         <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D126">
         <v>2</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="127" ht="14.25" spans="1:6">
@@ -3989,16 +3977,16 @@
         <v>9</v>
       </c>
       <c r="C127" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D127">
         <v>3</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="128" ht="14.25" spans="1:6">
@@ -4009,16 +3997,16 @@
         <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D128">
         <v>4</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="129" ht="14.25" spans="1:6">
@@ -4029,16 +4017,16 @@
         <v>9</v>
       </c>
       <c r="C129" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D129">
         <v>5</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="130" ht="14.25" spans="1:6">
@@ -4049,16 +4037,16 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D130">
         <v>6</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="131" ht="14.25" spans="1:6">
@@ -4069,16 +4057,16 @@
         <v>9</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D131">
         <v>7</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="132" ht="14.25" spans="1:6">
@@ -4089,16 +4077,16 @@
         <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D132">
         <v>8</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="133" ht="14.25" spans="1:6">
@@ -4109,16 +4097,16 @@
         <v>9</v>
       </c>
       <c r="C133" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D133">
         <v>9</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="134" ht="14.25" spans="1:6">
@@ -4129,16 +4117,16 @@
         <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D134">
         <v>10</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="135" ht="14.25" spans="1:6">
@@ -4149,16 +4137,16 @@
         <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D135">
         <v>11</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="136" ht="14.25" spans="1:6">
@@ -4169,16 +4157,16 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D136">
         <v>12</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="137" ht="14.25" spans="1:6">
@@ -4189,16 +4177,16 @@
         <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D137">
         <v>13</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138" ht="14.25" spans="1:6">
@@ -4209,16 +4197,16 @@
         <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D138">
         <v>14</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="139" ht="14.25" spans="1:6">
@@ -4229,16 +4217,16 @@
         <v>9</v>
       </c>
       <c r="C139" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D139">
         <v>15</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4249,13 +4237,13 @@
         <v>10</v>
       </c>
       <c r="C140" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4266,13 +4254,13 @@
         <v>10</v>
       </c>
       <c r="C141" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D141">
         <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4283,13 +4271,13 @@
         <v>10</v>
       </c>
       <c r="C142" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D142">
         <v>3</v>
       </c>
       <c r="E142" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4300,13 +4288,13 @@
         <v>10</v>
       </c>
       <c r="C143" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D143">
         <v>4</v>
       </c>
       <c r="E143" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4317,13 +4305,13 @@
         <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D144">
         <v>5</v>
       </c>
       <c r="E144" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4334,13 +4322,13 @@
         <v>10</v>
       </c>
       <c r="C145" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D145">
         <v>6</v>
       </c>
       <c r="E145" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4351,13 +4339,13 @@
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D146">
         <v>7</v>
       </c>
       <c r="E146" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4368,13 +4356,13 @@
         <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D147">
         <v>8</v>
       </c>
       <c r="E147" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4385,13 +4373,13 @@
         <v>10</v>
       </c>
       <c r="C148" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D148">
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4402,13 +4390,13 @@
         <v>10</v>
       </c>
       <c r="C149" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D149">
         <v>10</v>
       </c>
       <c r="E149" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4419,13 +4407,13 @@
         <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D150">
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4436,13 +4424,13 @@
         <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D151">
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4453,13 +4441,13 @@
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D152">
         <v>13</v>
       </c>
       <c r="E152" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4470,13 +4458,13 @@
         <v>10</v>
       </c>
       <c r="C153" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D153">
         <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4487,13 +4475,13 @@
         <v>10</v>
       </c>
       <c r="C154" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D154">
         <v>15</v>
       </c>
       <c r="E154" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4504,13 +4492,13 @@
         <v>11</v>
       </c>
       <c r="C155" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4521,13 +4509,13 @@
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D156">
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -4538,13 +4526,13 @@
         <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D157">
         <v>3</v>
       </c>
       <c r="E157" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -4555,13 +4543,13 @@
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D158">
         <v>4</v>
       </c>
       <c r="E158" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -4572,13 +4560,13 @@
         <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D159">
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4589,13 +4577,13 @@
         <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D160">
         <v>6</v>
       </c>
       <c r="E160" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -4606,13 +4594,13 @@
         <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D161">
         <v>7</v>
       </c>
       <c r="E161" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4623,13 +4611,13 @@
         <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D162">
         <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4640,13 +4628,13 @@
         <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D163">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4657,13 +4645,13 @@
         <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D164">
         <v>10</v>
       </c>
       <c r="E164" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4674,13 +4662,13 @@
         <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D165">
         <v>11</v>
       </c>
       <c r="E165" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4691,13 +4679,13 @@
         <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D166">
         <v>12</v>
       </c>
       <c r="E166" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4708,13 +4696,13 @@
         <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D167">
         <v>13</v>
       </c>
       <c r="E167" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4725,13 +4713,13 @@
         <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D168">
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4742,13 +4730,13 @@
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D169">
         <v>15</v>
       </c>
       <c r="E169" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4759,13 +4747,13 @@
         <v>12</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4776,13 +4764,13 @@
         <v>12</v>
       </c>
       <c r="C171" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D171">
         <v>2</v>
       </c>
       <c r="E171" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4793,13 +4781,13 @@
         <v>12</v>
       </c>
       <c r="C172" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D172">
         <v>3</v>
       </c>
       <c r="E172" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4810,13 +4798,13 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D173">
         <v>4</v>
       </c>
       <c r="E173" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4827,13 +4815,13 @@
         <v>12</v>
       </c>
       <c r="C174" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D174">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4844,13 +4832,13 @@
         <v>12</v>
       </c>
       <c r="C175" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D175">
         <v>6</v>
       </c>
       <c r="E175" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4861,13 +4849,13 @@
         <v>12</v>
       </c>
       <c r="C176" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D176">
         <v>7</v>
       </c>
       <c r="E176" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -4878,13 +4866,13 @@
         <v>12</v>
       </c>
       <c r="C177" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D177">
         <v>8</v>
       </c>
       <c r="E177" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -4895,13 +4883,13 @@
         <v>12</v>
       </c>
       <c r="C178" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D178">
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -4912,13 +4900,13 @@
         <v>12</v>
       </c>
       <c r="C179" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D179">
         <v>10</v>
       </c>
       <c r="E179" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -4929,13 +4917,13 @@
         <v>12</v>
       </c>
       <c r="C180" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D180">
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -4946,13 +4934,13 @@
         <v>12</v>
       </c>
       <c r="C181" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D181">
         <v>12</v>
       </c>
       <c r="E181" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -4963,13 +4951,13 @@
         <v>12</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D182">
         <v>13</v>
       </c>
       <c r="E182" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -4980,13 +4968,13 @@
         <v>12</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D183">
         <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -4997,13 +4985,13 @@
         <v>12</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D184">
         <v>15</v>
       </c>
       <c r="E184" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="185" ht="14.25" spans="1:9">
@@ -5014,13 +5002,13 @@
         <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D185">
         <v>1</v>
       </c>
       <c r="E185" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I185" s="6"/>
     </row>
@@ -5032,13 +5020,13 @@
         <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D186">
         <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I186" s="6"/>
     </row>
@@ -5050,13 +5038,13 @@
         <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D187">
         <v>3</v>
       </c>
       <c r="E187" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I187" s="6"/>
     </row>
@@ -5068,13 +5056,13 @@
         <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D188">
         <v>4</v>
       </c>
       <c r="E188" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I188" s="6"/>
     </row>
@@ -5086,13 +5074,13 @@
         <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D189">
         <v>5</v>
       </c>
       <c r="E189" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I189" s="6"/>
     </row>
@@ -5104,13 +5092,13 @@
         <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D190">
         <v>6</v>
       </c>
       <c r="E190" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I190" s="6"/>
     </row>
@@ -5122,13 +5110,13 @@
         <v>13</v>
       </c>
       <c r="C191" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D191">
         <v>7</v>
       </c>
       <c r="E191" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I191" s="6"/>
     </row>
@@ -5140,13 +5128,13 @@
         <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D192">
         <v>8</v>
       </c>
       <c r="E192" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I192" s="6"/>
     </row>
@@ -5158,13 +5146,13 @@
         <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D193">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I193" s="6"/>
     </row>
@@ -5176,13 +5164,13 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D194">
         <v>10</v>
       </c>
       <c r="E194" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I194" s="6"/>
     </row>
@@ -5194,13 +5182,13 @@
         <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D195">
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I195" s="6"/>
     </row>
@@ -5212,13 +5200,13 @@
         <v>13</v>
       </c>
       <c r="C196" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D196">
         <v>12</v>
       </c>
       <c r="E196" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I196" s="7"/>
     </row>
@@ -5230,13 +5218,13 @@
         <v>13</v>
       </c>
       <c r="C197" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D197">
         <v>13</v>
       </c>
       <c r="E197" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I197" s="7"/>
     </row>
@@ -5248,13 +5236,13 @@
         <v>13</v>
       </c>
       <c r="C198" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D198">
         <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I198" s="7"/>
     </row>
@@ -5266,13 +5254,13 @@
         <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D199">
         <v>15</v>
       </c>
       <c r="E199" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I199" s="8"/>
     </row>
@@ -5284,13 +5272,13 @@
         <v>14</v>
       </c>
       <c r="C200" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D200">
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -5301,13 +5289,13 @@
         <v>14</v>
       </c>
       <c r="C201" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D201">
         <v>2</v>
       </c>
       <c r="E201" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -5318,13 +5306,13 @@
         <v>14</v>
       </c>
       <c r="C202" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D202">
         <v>3</v>
       </c>
       <c r="E202" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -5335,13 +5323,13 @@
         <v>14</v>
       </c>
       <c r="C203" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D203">
         <v>4</v>
       </c>
       <c r="E203" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -5352,13 +5340,13 @@
         <v>14</v>
       </c>
       <c r="C204" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D204">
         <v>5</v>
       </c>
       <c r="E204" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -5369,13 +5357,13 @@
         <v>14</v>
       </c>
       <c r="C205" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D205">
         <v>6</v>
       </c>
       <c r="E205" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -5386,13 +5374,13 @@
         <v>14</v>
       </c>
       <c r="C206" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D206">
         <v>7</v>
       </c>
       <c r="E206" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -5403,13 +5391,13 @@
         <v>14</v>
       </c>
       <c r="C207" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D207">
         <v>8</v>
       </c>
       <c r="E207" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -5420,13 +5408,13 @@
         <v>14</v>
       </c>
       <c r="C208" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D208">
         <v>9</v>
       </c>
       <c r="E208" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -5437,13 +5425,13 @@
         <v>14</v>
       </c>
       <c r="C209" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D209">
         <v>10</v>
       </c>
       <c r="E209" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -5454,13 +5442,13 @@
         <v>14</v>
       </c>
       <c r="C210" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D210">
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -5471,13 +5459,13 @@
         <v>14</v>
       </c>
       <c r="C211" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D211">
         <v>12</v>
       </c>
       <c r="E211" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -5488,13 +5476,13 @@
         <v>14</v>
       </c>
       <c r="C212" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D212">
         <v>13</v>
       </c>
       <c r="E212" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5505,13 +5493,13 @@
         <v>14</v>
       </c>
       <c r="C213" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D213">
         <v>14</v>
       </c>
       <c r="E213" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -5522,13 +5510,13 @@
         <v>14</v>
       </c>
       <c r="C214" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D214">
         <v>15</v>
       </c>
       <c r="E214" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5539,13 +5527,13 @@
         <v>15</v>
       </c>
       <c r="C215" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -5556,13 +5544,13 @@
         <v>15</v>
       </c>
       <c r="C216" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D216">
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -5573,13 +5561,13 @@
         <v>15</v>
       </c>
       <c r="C217" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D217">
         <v>3</v>
       </c>
       <c r="E217" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -5590,13 +5578,13 @@
         <v>15</v>
       </c>
       <c r="C218" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D218">
         <v>4</v>
       </c>
       <c r="E218" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5607,13 +5595,13 @@
         <v>15</v>
       </c>
       <c r="C219" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D219">
         <v>5</v>
       </c>
       <c r="E219" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -5624,13 +5612,13 @@
         <v>15</v>
       </c>
       <c r="C220" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D220">
         <v>6</v>
       </c>
       <c r="E220" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -5641,13 +5629,13 @@
         <v>15</v>
       </c>
       <c r="C221" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D221">
         <v>7</v>
       </c>
       <c r="E221" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -5658,13 +5646,13 @@
         <v>15</v>
       </c>
       <c r="C222" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D222">
         <v>8</v>
       </c>
       <c r="E222" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -5675,13 +5663,13 @@
         <v>15</v>
       </c>
       <c r="C223" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D223">
         <v>9</v>
       </c>
       <c r="E223" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -5692,13 +5680,13 @@
         <v>15</v>
       </c>
       <c r="C224" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D224">
         <v>10</v>
       </c>
       <c r="E224" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -5709,13 +5697,13 @@
         <v>15</v>
       </c>
       <c r="C225" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D225">
         <v>11</v>
       </c>
       <c r="E225" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -5726,13 +5714,13 @@
         <v>15</v>
       </c>
       <c r="C226" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D226">
         <v>12</v>
       </c>
       <c r="E226" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5743,13 +5731,13 @@
         <v>15</v>
       </c>
       <c r="C227" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D227">
         <v>13</v>
       </c>
       <c r="E227" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5760,13 +5748,13 @@
         <v>15</v>
       </c>
       <c r="C228" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D228">
         <v>14</v>
       </c>
       <c r="E228" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5777,13 +5765,13 @@
         <v>15</v>
       </c>
       <c r="C229" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D229">
         <v>15</v>
       </c>
       <c r="E229" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5794,7 +5782,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -5808,7 +5796,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D231">
         <v>2</v>
@@ -5822,7 +5810,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D232">
         <v>3</v>
@@ -5836,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D233">
         <v>4</v>
@@ -5850,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D234">
         <v>5</v>
@@ -5864,7 +5852,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D235">
         <v>6</v>
@@ -5878,7 +5866,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D236">
         <v>7</v>
@@ -5892,7 +5880,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D237">
         <v>8</v>
@@ -5906,7 +5894,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D238">
         <v>9</v>
@@ -5920,7 +5908,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D239">
         <v>10</v>
@@ -5934,7 +5922,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D240">
         <v>11</v>
@@ -5948,7 +5936,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D241">
         <v>12</v>
@@ -5962,7 +5950,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D242">
         <v>13</v>
@@ -5976,7 +5964,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D243">
         <v>14</v>
@@ -5990,7 +5978,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D244">
         <v>15</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenGroup.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_strengthenGroup.xlsx
@@ -365,49 +365,49 @@
     <t>首饰强化（攻击）</t>
   </si>
   <si>
-    <t>200011#1|200021#2</t>
-  </si>
-  <si>
-    <t>200011#1|200021#4</t>
-  </si>
-  <si>
-    <t>200011#2|200021#5</t>
-  </si>
-  <si>
-    <t>200011#2|200021#6</t>
-  </si>
-  <si>
-    <t>200011#3|200021#7</t>
-  </si>
-  <si>
-    <t>200011#4|200021#8</t>
-  </si>
-  <si>
-    <t>200011#5|200021#9</t>
-  </si>
-  <si>
-    <t>200011#6|200021#10</t>
-  </si>
-  <si>
-    <t>200011#7|200021#11</t>
-  </si>
-  <si>
-    <t>200011#8|200021#13</t>
-  </si>
-  <si>
-    <t>200011#10|200021#15</t>
-  </si>
-  <si>
-    <t>200011#11|200021#17</t>
-  </si>
-  <si>
-    <t>200011#12|200021#19</t>
-  </si>
-  <si>
-    <t>200011#13|200021#21</t>
-  </si>
-  <si>
-    <t>200011#14|200021#23</t>
+    <t>200041#2</t>
+  </si>
+  <si>
+    <t>200041#4</t>
+  </si>
+  <si>
+    <t>200041#6</t>
+  </si>
+  <si>
+    <t>200041#8</t>
+  </si>
+  <si>
+    <t>200041#10</t>
+  </si>
+  <si>
+    <t>200041#12</t>
+  </si>
+  <si>
+    <t>200041#14</t>
+  </si>
+  <si>
+    <t>200041#16</t>
+  </si>
+  <si>
+    <t>200041#18</t>
+  </si>
+  <si>
+    <t>200041#23</t>
+  </si>
+  <si>
+    <t>200041#28</t>
+  </si>
+  <si>
+    <t>200041#38</t>
+  </si>
+  <si>
+    <t>200041#50</t>
+  </si>
+  <si>
+    <t>200041#66</t>
+  </si>
+  <si>
+    <t>200041#88</t>
   </si>
   <si>
     <t>翅膀强化类型1</t>
@@ -5774,7 +5774,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" ht="14.25" spans="1:5">
       <c r="A230">
         <v>16001</v>
       </c>
@@ -5787,8 +5787,9 @@
       <c r="D230">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" ht="14.25" spans="1:5">
       <c r="A231">
         <v>16002</v>
       </c>
@@ -5801,8 +5802,9 @@
       <c r="D231">
         <v>2</v>
       </c>
-    </row>
-    <row r="232" spans="1:5">
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" ht="14.25" spans="1:5">
       <c r="A232">
         <v>16003</v>
       </c>
@@ -5815,8 +5817,9 @@
       <c r="D232">
         <v>3</v>
       </c>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" ht="14.25" spans="1:5">
       <c r="A233">
         <v>16004</v>
       </c>
@@ -5829,8 +5832,9 @@
       <c r="D233">
         <v>4</v>
       </c>
-    </row>
-    <row r="234" spans="1:5">
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" ht="14.25" spans="1:5">
       <c r="A234">
         <v>16005</v>
       </c>
@@ -5843,8 +5847,9 @@
       <c r="D234">
         <v>5</v>
       </c>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" ht="14.25" spans="1:5">
       <c r="A235">
         <v>16006</v>
       </c>
@@ -5857,8 +5862,9 @@
       <c r="D235">
         <v>6</v>
       </c>
-    </row>
-    <row r="236" spans="1:5">
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" ht="14.25" spans="1:5">
       <c r="A236">
         <v>16007</v>
       </c>
@@ -5871,8 +5877,9 @@
       <c r="D236">
         <v>7</v>
       </c>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" ht="14.25" spans="1:5">
       <c r="A237">
         <v>16008</v>
       </c>
@@ -5885,8 +5892,9 @@
       <c r="D237">
         <v>8</v>
       </c>
-    </row>
-    <row r="238" spans="1:5">
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" ht="14.25" spans="1:5">
       <c r="A238">
         <v>16009</v>
       </c>
@@ -5899,8 +5907,9 @@
       <c r="D238">
         <v>9</v>
       </c>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" ht="14.25" spans="1:5">
       <c r="A239">
         <v>16010</v>
       </c>
@@ -5913,8 +5922,9 @@
       <c r="D239">
         <v>10</v>
       </c>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" ht="14.25" spans="1:5">
       <c r="A240">
         <v>16011</v>
       </c>
@@ -5927,8 +5937,9 @@
       <c r="D240">
         <v>11</v>
       </c>
-    </row>
-    <row r="241" spans="1:4">
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" ht="14.25" spans="1:5">
       <c r="A241">
         <v>16012</v>
       </c>
@@ -5941,8 +5952,9 @@
       <c r="D241">
         <v>12</v>
       </c>
-    </row>
-    <row r="242" spans="1:4">
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" ht="14.25" spans="1:5">
       <c r="A242">
         <v>16013</v>
       </c>
@@ -5955,8 +5967,9 @@
       <c r="D242">
         <v>13</v>
       </c>
-    </row>
-    <row r="243" spans="1:4">
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" ht="14.25" spans="1:5">
       <c r="A243">
         <v>16014</v>
       </c>
@@ -5969,8 +5982,9 @@
       <c r="D243">
         <v>14</v>
       </c>
-    </row>
-    <row r="244" spans="1:4">
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" ht="14.25" spans="1:5">
       <c r="A244">
         <v>16015</v>
       </c>
@@ -5983,6 +5997,7 @@
       <c r="D244">
         <v>15</v>
       </c>
+      <c r="E244" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
